--- a/docs/PRAP_Development_Plan_v2.38.xlsx
+++ b/docs/PRAP_Development_Plan_v2.38.xlsx
@@ -7386,7 +7386,7 @@
       </c>
       <c r="E21" s="18" t="inlineStr">
         <is>
-          <t>R-30, REQ-CAL-18, SCHEMA 9: A FIGURE CAN BE STATED INSTEAD OF CALCULATED. Until now every monthly FTE came from the assumptions, and on a project two years in that is often the worse of the two available answers - the manager knows what the rest of it takes, and a standard period weight multiplied by a standard role factor does not. Project and Assignment each gain estimation_type ('automatic' or 'manual'), and a new sheet MonthlyEstimate carries the stated figures, keyed on (scope, ref_id, month) so one sheet serves both levels. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution and replaces the multiplication outright; a PROJECT figure is the whole month, and the people on it are SCALED so they still add up to it - chosen over the alternatives because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one real guarantee. The scaling factor is recorded on every line, so a person whose figure moved without anything of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies EVERY month across from the figures currently on screen, so nothing jumps, and switching back discards the lot. That was chosen over per-month marking deliberately - once a figure has been edited, 'which months are still automatic' has no useful answer, because those would still move under a plan somebody has signed off whenever an assumption changed. What the user takes on in exchange is responsibility for all of them, and the confirmation says so in those words. EVERY CHANGE OF CALCULATION WAY IS CONFIRMED, in both directions, and typing 'manual' into the cell opens the same dialog rather than setting the flag - the flag without the copy would count every month as 0.00, which is the one change in the application that could silently zero a figure. V-31 reports a manual thing with a month carrying no figure; V-32 a project figure in a month nobody is assigned to, which cannot be shared out and is therefore NOT applied. Both are raised from the calculation, like V-23, because they are things that happened to a number. The stated figures round-trip through the source export, and the results export gains four columns - estimation, automatic_fte, project_manual_total, project_scale - so a reader can see which rows were stated, at which level, and what the assumptions would have said instead. Nothing moves on a file that uses none of it: test_app.py's four-way comparison agrees on all 1,227 and 441 person-months, and both dummy sets now carry a manual project and a manual assignment so the rule is under that comparison rather than in one unit test.</t>
+          <t>R-30, REQ-CAL-18, SCHEMA 9: A FIGURE CAN BE STATED INSTEAD OF CALCULATED. Until now every monthly FTE came from the assumptions, and on a project two years in that is often the worse of the two available answers - the manager knows what the rest of it takes, and a standard period weight multiplied by a standard role factor does not. Project and Assignment each gain estimation_type ('automatic' or 'manual'), and a new sheet MonthlyEstimate carries the stated figures, keyed on (scope, ref_id, month) so one sheet serves both levels. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution and replaces the multiplication outright; a PROJECT figure is the whole month, and the people on it are SCALED so they still add up to it - chosen over the alternatives because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one real guarantee. The scaling factor is recorded on every line, so a person whose figure moved without anything of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies EVERY month across from the figures currently on screen - to TWO DECIMAL PLACES, because a stated figure is one somebody reads and edits and 0.01 FTE is already 1.6 hours, so a month can move by up to 0.005 FTE at the moment of switching - so nothing jumps, and switching back discards the lot. That was chosen over per-month marking deliberately - once a figure has been edited, 'which months are still automatic' has no useful answer, because those would still move under a plan somebody has signed off whenever an assumption changed. What the user takes on in exchange is responsibility for all of them, and the confirmation says so in those words. EVERY CHANGE OF CALCULATION WAY IS CONFIRMED, in both directions, and typing 'manual' into the cell opens the same dialog rather than setting the flag - the flag without the copy would count every month as 0.00, which is the one change in the application that could silently zero a figure. V-31 reports a manual thing with a month carrying no figure; V-32 a project figure in a month nobody is assigned to, which cannot be shared out and is therefore NOT applied. Both are raised from the calculation, like V-23, because they are things that happened to a number. The stated figures round-trip through the source export, and the results export gains four columns - estimation, automatic_fte, project_manual_total, project_scale - so a reader can see which rows were stated, at which level, and what the assumptions would have said instead. Nothing moves on a file that uses none of it: test_app.py's four-way comparison agrees on all 1,227 and 441 person-months, and both dummy sets now carry a manual project and a manual assignment so the rule is under that comparison rather than in one unit test.</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>A PROJECT, OR ONE ASSIGNMENT, MAY HAVE ITS MONTHLY FTE STATED RATHER THAN CALCULATED. estimation_type on Project and on Assignment selects which; MonthlyEstimate carries the stated figures. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution to that project and replaces the multiplication outright; a PROJECT figure is the whole month, and every person on it that month is SCALED so they still add up to it - because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one guarantee. The scaling factor is recorded on every line, so a person whose figure moved with nothing of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies every month across from the figures currently on screen, so nothing jumps, and switching back discards them all. Per-month marking was considered and rejected - once a figure has been edited, months still calculated would keep moving under a signed-off plan whenever an assumption changed, and 'which months are mine' has no useful answer. Every change of calculation way is CONFIRMED, in both directions. A project figure in a month nobody is assigned to cannot be shared out and is NOT applied (V-32); a manual thing with a month carrying no figure counts that month as 0.00 and V-31 says so.</t>
+          <t>A PROJECT, OR ONE ASSIGNMENT, MAY HAVE ITS MONTHLY FTE STATED RATHER THAN CALCULATED. estimation_type on Project and on Assignment selects which; MonthlyEstimate carries the stated figures. TWO LEVELS, applied in that order: an ASSIGNMENT figure IS that person's contribution to that project and replaces the multiplication outright; a PROJECT figure is the whole month, and every person on it that month is SCALED so they still add up to it - because a project total that did not equal the sum of its people would put the two utilisation charts in disagreement and cost the results export its one guarantee. The scaling factor is recorded on every line, so a person whose figure moved with nothing of their own changing can find out why. MANUAL IS ALL OR NOTHING for the thing it is set on: switching copies every month across from the figures currently on screen, so nothing jumps, and switching back discards them all. The copy is written to TWO DECIMAL PLACES: a stated figure lands in a cell somebody reads and edits, and two places is the finest edit that means anything in the unit people think in - at 160 hours to the FTE, 0.01 is 1.6 hours. A month can therefore move by up to 0.005 FTE, about 48 minutes, at the moment of switching. Per-month marking was considered and rejected - once a figure has been edited, months still calculated would keep moving under a signed-off plan whenever an assumption changed, and 'which months are mine' has no useful answer. Every change of calculation way is CONFIRMED, in both directions. A project figure in a month nobody is assigned to cannot be shared out and is NOT applied (V-32); a manual thing with a month carrying no figure counts that month as 0.00 and V-31 says so.</t>
         </is>
       </c>
       <c r="D33" s="17" t="inlineStr">
